--- a/selenium_automation/reports/Excel/Passed_Test_Cases.xlsx
+++ b/selenium_automation/reports/Excel/Passed_Test_Cases.xlsx
@@ -55,306 +55,309 @@
     <t>Verify login fails with invalid password</t>
   </si>
   <si>
+    <t>TC_WEB_AUTH_003</t>
+  </si>
+  <si>
+    <t>Verify login fails with unregistered email address</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_004</t>
+  </si>
+  <si>
+    <t>Verify password field masks input characters</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_005</t>
+  </si>
+  <si>
+    <t>Verify 'Remember Me' functionality persists session</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_006</t>
+  </si>
+  <si>
+    <t>Verify OTP generation on 2FA enabled account</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_007</t>
+  </si>
+  <si>
+    <t>Verify OTP verification with valid 6-digit code</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_008</t>
+  </si>
+  <si>
+    <t>Verify OTP verification fails on expired code</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_009</t>
+  </si>
+  <si>
+    <t>Verify account lockout after 5 consecutive failed attempts</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_010</t>
+  </si>
+  <si>
+    <t>Verify 'Forgot Password' link sends password reset email</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_011</t>
+  </si>
+  <si>
+    <t>Verify password reset token validation and expiration</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_012</t>
+  </si>
+  <si>
+    <t>Verify password reset with strong password policy</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_013</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth single sign-on redirect</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_014</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth token exchange and session creation</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_015</t>
+  </si>
+  <si>
+    <t>Verify user logout invalidates active auth token</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_016</t>
+  </si>
+  <si>
+    <t>Verify protected route redirection to login when unauthenticated</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_017</t>
+  </si>
+  <si>
+    <t>Verify SQL injection attempt in login email field is blocked</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_018</t>
+  </si>
+  <si>
+    <t>Verify XSS payload in login username field is sanitized</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_019</t>
+  </si>
+  <si>
+    <t>Verify session cookie has HttpOnly and Secure flags</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_020</t>
+  </si>
+  <si>
+    <t>Verify login page SSL/TLS certificate validity</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_021</t>
+  </si>
+  <si>
+    <t>Verify user login with valid email and password (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_022</t>
+  </si>
+  <si>
+    <t>Verify login fails with invalid password (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_023</t>
+  </si>
+  <si>
+    <t>Verify login fails with unregistered email address (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_024</t>
+  </si>
+  <si>
+    <t>Verify password field masks input characters (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_025</t>
+  </si>
+  <si>
+    <t>Verify 'Remember Me' functionality persists session (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_026</t>
+  </si>
+  <si>
+    <t>Verify OTP generation on 2FA enabled account (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_027</t>
+  </si>
+  <si>
+    <t>Verify OTP verification with valid 6-digit code (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_028</t>
+  </si>
+  <si>
+    <t>Verify OTP verification fails on expired code (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_029</t>
+  </si>
+  <si>
+    <t>Verify account lockout after 5 consecutive failed attempts (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_030</t>
+  </si>
+  <si>
+    <t>Verify 'Forgot Password' link sends password reset email (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_031</t>
+  </si>
+  <si>
+    <t>Verify password reset token validation and expiration (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_032</t>
+  </si>
+  <si>
+    <t>Verify password reset with strong password policy (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_033</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth single sign-on redirect (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_034</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth token exchange and session creation (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_035</t>
+  </si>
+  <si>
+    <t>Verify user logout invalidates active auth token (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_036</t>
+  </si>
+  <si>
+    <t>Verify protected route redirection to login when unauthenticated (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_037</t>
+  </si>
+  <si>
+    <t>Verify SQL injection attempt in login email field is blocked (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_038</t>
+  </si>
+  <si>
+    <t>Verify XSS payload in login username field is sanitized (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_039</t>
+  </si>
+  <si>
+    <t>Verify session cookie has HttpOnly and Secure flags (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_040</t>
+  </si>
+  <si>
+    <t>Verify login page SSL/TLS certificate validity (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_001</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>Verify admin user access to Admin Panel dashboard</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_002</t>
+  </si>
+  <si>
+    <t>Verify regular donor is denied access to /admin route</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_003</t>
+  </si>
+  <si>
+    <t>Verify hospital staff can access blood inventory update view</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_004</t>
+  </si>
+  <si>
+    <t>Verify recipient cannot edit blood camp schedules without organizer role</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_005</t>
+  </si>
+  <si>
+    <t>Verify super-admin role can manage hospital credentials</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_006</t>
+  </si>
+  <si>
+    <t>Verify JWT role claim tampering is rejected with 403 Forbidden</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_007</t>
+  </si>
+  <si>
+    <t>Verify IDOR prevention when donor accesses another donor's private profile</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_008</t>
+  </si>
+  <si>
+    <t>Verify blood request approval restricted to authorized medical officers</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_009</t>
+  </si>
+  <si>
+    <t>Verify donor cannot view private medical notes of other donors</t>
+  </si>
+  <si>
     <t>0.01</t>
   </si>
   <si>
-    <t>TC_WEB_AUTH_003</t>
-  </si>
-  <si>
-    <t>Verify login fails with unregistered email address</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_004</t>
-  </si>
-  <si>
-    <t>Verify password field masks input characters</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_005</t>
-  </si>
-  <si>
-    <t>Verify 'Remember Me' functionality persists session</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_006</t>
-  </si>
-  <si>
-    <t>Verify OTP generation on 2FA enabled account</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_007</t>
-  </si>
-  <si>
-    <t>Verify OTP verification with valid 6-digit code</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_008</t>
-  </si>
-  <si>
-    <t>Verify OTP verification fails on expired code</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_009</t>
-  </si>
-  <si>
-    <t>Verify account lockout after 5 consecutive failed attempts</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_010</t>
-  </si>
-  <si>
-    <t>Verify 'Forgot Password' link sends password reset email</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_011</t>
-  </si>
-  <si>
-    <t>Verify password reset token validation and expiration</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_012</t>
-  </si>
-  <si>
-    <t>Verify password reset with strong password policy</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_013</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth single sign-on redirect</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_014</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth token exchange and session creation</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_015</t>
-  </si>
-  <si>
-    <t>Verify user logout invalidates active auth token</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_016</t>
-  </si>
-  <si>
-    <t>Verify protected route redirection to login when unauthenticated</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_017</t>
-  </si>
-  <si>
-    <t>Verify SQL injection attempt in login email field is blocked</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_018</t>
-  </si>
-  <si>
-    <t>Verify XSS payload in login username field is sanitized</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_019</t>
-  </si>
-  <si>
-    <t>Verify session cookie has HttpOnly and Secure flags</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_020</t>
-  </si>
-  <si>
-    <t>Verify login page SSL/TLS certificate validity</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_021</t>
-  </si>
-  <si>
-    <t>Verify user login with valid email and password (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_022</t>
-  </si>
-  <si>
-    <t>Verify login fails with invalid password (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_023</t>
-  </si>
-  <si>
-    <t>Verify login fails with unregistered email address (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_024</t>
-  </si>
-  <si>
-    <t>Verify password field masks input characters (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_025</t>
-  </si>
-  <si>
-    <t>Verify 'Remember Me' functionality persists session (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_026</t>
-  </si>
-  <si>
-    <t>Verify OTP generation on 2FA enabled account (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_027</t>
-  </si>
-  <si>
-    <t>Verify OTP verification with valid 6-digit code (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_028</t>
-  </si>
-  <si>
-    <t>Verify OTP verification fails on expired code (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_029</t>
-  </si>
-  <si>
-    <t>Verify account lockout after 5 consecutive failed attempts (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_030</t>
-  </si>
-  <si>
-    <t>Verify 'Forgot Password' link sends password reset email (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_031</t>
-  </si>
-  <si>
-    <t>Verify password reset token validation and expiration (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_032</t>
-  </si>
-  <si>
-    <t>Verify password reset with strong password policy (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_033</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth single sign-on redirect (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_034</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth token exchange and session creation (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_035</t>
-  </si>
-  <si>
-    <t>Verify user logout invalidates active auth token (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_036</t>
-  </si>
-  <si>
-    <t>Verify protected route redirection to login when unauthenticated (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_037</t>
-  </si>
-  <si>
-    <t>Verify SQL injection attempt in login email field is blocked (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_038</t>
-  </si>
-  <si>
-    <t>Verify XSS payload in login username field is sanitized (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_039</t>
-  </si>
-  <si>
-    <t>Verify session cookie has HttpOnly and Secure flags (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_040</t>
-  </si>
-  <si>
-    <t>Verify login page SSL/TLS certificate validity (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_001</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Verify admin user access to Admin Panel dashboard</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_002</t>
-  </si>
-  <si>
-    <t>Verify regular donor is denied access to /admin route</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_003</t>
-  </si>
-  <si>
-    <t>Verify hospital staff can access blood inventory update view</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_004</t>
-  </si>
-  <si>
-    <t>Verify recipient cannot edit blood camp schedules without organizer role</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_005</t>
-  </si>
-  <si>
-    <t>Verify super-admin role can manage hospital credentials</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_006</t>
-  </si>
-  <si>
-    <t>Verify JWT role claim tampering is rejected with 403 Forbidden</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_007</t>
-  </si>
-  <si>
-    <t>Verify IDOR prevention when donor accesses another donor's private profile</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_008</t>
-  </si>
-  <si>
-    <t>Verify blood request approval restricted to authorized medical officers</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_009</t>
-  </si>
-  <si>
-    <t>Verify donor cannot view private medical notes of other donors</t>
-  </si>
-  <si>
     <t>TC_WEB_AUTHZ_010</t>
   </si>
   <si>
@@ -467,9 +470,6 @@
   </si>
   <si>
     <t>Verify blood request approval restricted to authorized medical officers (Variation 3 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>0.05</t>
   </si>
   <si>
     <t>TC_WEB_AUTHZ_029</t>
@@ -3424,7 +3424,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -3432,19 +3432,19 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -3484,7 +3484,7 @@
         <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -3492,13 +3492,13 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>9</v>
@@ -3512,19 +3512,19 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
@@ -3532,13 +3532,13 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -3552,19 +3552,19 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -3572,19 +3572,19 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -3592,16 +3592,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>21</v>
@@ -3612,19 +3612,19 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -3632,19 +3632,19 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -3652,19 +3652,19 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -3672,19 +3672,19 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
@@ -3692,19 +3692,19 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -3712,19 +3712,19 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -3732,19 +3732,19 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -3752,16 +3752,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
@@ -3772,19 +3772,19 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -3792,19 +3792,19 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -3812,19 +3812,19 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -3832,19 +3832,19 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>11</v>
@@ -3852,19 +3852,19 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>11</v>
@@ -3872,19 +3872,19 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>11</v>
@@ -3892,19 +3892,19 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -3912,19 +3912,19 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -3944,7 +3944,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -3964,7 +3964,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>11</v>
@@ -3984,7 +3984,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -4001,10 +4001,10 @@
         <v>76</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>11</v>
@@ -4024,7 +4024,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -4044,7 +4044,7 @@
         <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
@@ -4064,7 +4064,7 @@
         <v>9</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -4081,7 +4081,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>21</v>
@@ -4104,7 +4104,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>11</v>
@@ -4124,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>11</v>
@@ -4144,7 +4144,7 @@
         <v>9</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>11</v>
@@ -4161,10 +4161,10 @@
         <v>92</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>11</v>
@@ -4184,7 +4184,7 @@
         <v>20</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>11</v>
@@ -4204,7 +4204,7 @@
         <v>9</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -4241,10 +4241,10 @@
         <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -4261,10 +4261,10 @@
         <v>103</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -4284,7 +4284,7 @@
         <v>9</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -4304,7 +4304,7 @@
         <v>9</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -4321,10 +4321,10 @@
         <v>109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -4341,10 +4341,10 @@
         <v>111</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -4364,7 +4364,7 @@
         <v>9</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -4372,13 +4372,13 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>9</v>
@@ -4392,16 +4392,16 @@
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>21</v>
@@ -4412,19 +4412,19 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>11</v>
@@ -4432,19 +4432,19 @@
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>11</v>
@@ -4452,19 +4452,19 @@
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -4472,16 +4472,16 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>21</v>
@@ -4492,19 +4492,19 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>11</v>
@@ -4512,19 +4512,19 @@
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -4532,19 +4532,19 @@
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
@@ -4552,19 +4552,19 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>11</v>
@@ -4572,19 +4572,19 @@
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>11</v>
@@ -4592,19 +4592,19 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>11</v>
@@ -4612,19 +4612,19 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>11</v>
@@ -4632,19 +4632,19 @@
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>11</v>
@@ -4652,19 +4652,19 @@
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>11</v>
@@ -4672,19 +4672,19 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>11</v>
@@ -4692,19 +4692,19 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>11</v>
@@ -4712,19 +4712,19 @@
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>11</v>
@@ -4732,19 +4732,19 @@
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>11</v>
@@ -4764,7 +4764,7 @@
         <v>9</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>11</v>
@@ -4801,10 +4801,10 @@
         <v>158</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>11</v>
@@ -4821,10 +4821,10 @@
         <v>160</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>11</v>
@@ -4844,7 +4844,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>11</v>
@@ -4864,7 +4864,7 @@
         <v>9</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -4881,10 +4881,10 @@
         <v>166</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>11</v>
@@ -4901,10 +4901,10 @@
         <v>168</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>11</v>
@@ -4924,7 +4924,7 @@
         <v>9</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>11</v>
@@ -4961,10 +4961,10 @@
         <v>174</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>11</v>
@@ -4981,10 +4981,10 @@
         <v>176</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>11</v>
@@ -5001,10 +5001,10 @@
         <v>179</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>11</v>
@@ -5021,10 +5021,10 @@
         <v>181</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>11</v>
@@ -5044,7 +5044,7 @@
         <v>20</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>11</v>
@@ -5064,7 +5064,7 @@
         <v>9</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -5081,7 +5081,7 @@
         <v>187</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>10</v>
@@ -5101,10 +5101,10 @@
         <v>189</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>11</v>
@@ -5144,7 +5144,7 @@
         <v>9</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -5161,10 +5161,10 @@
         <v>195</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -5181,10 +5181,10 @@
         <v>197</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -5224,7 +5224,7 @@
         <v>9</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>11</v>
@@ -5241,10 +5241,10 @@
         <v>203</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>11</v>
@@ -5261,10 +5261,10 @@
         <v>205</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>11</v>
@@ -5284,7 +5284,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>11</v>
@@ -5304,7 +5304,7 @@
         <v>9</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>11</v>
@@ -5321,10 +5321,10 @@
         <v>211</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>11</v>
@@ -5341,10 +5341,10 @@
         <v>213</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>11</v>
@@ -5364,7 +5364,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>11</v>
@@ -5384,7 +5384,7 @@
         <v>9</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>11</v>
@@ -5401,10 +5401,10 @@
         <v>219</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -5421,10 +5421,10 @@
         <v>221</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>11</v>
@@ -5444,7 +5444,7 @@
         <v>20</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -5481,10 +5481,10 @@
         <v>227</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>11</v>
@@ -5501,10 +5501,10 @@
         <v>229</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>11</v>
@@ -5524,7 +5524,7 @@
         <v>20</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>11</v>
@@ -5544,7 +5544,7 @@
         <v>9</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>11</v>
@@ -5561,10 +5561,10 @@
         <v>235</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>11</v>
@@ -5581,7 +5581,7 @@
         <v>237</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>21</v>
@@ -5601,10 +5601,10 @@
         <v>240</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>11</v>
@@ -5624,7 +5624,7 @@
         <v>20</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>11</v>
@@ -5641,10 +5641,10 @@
         <v>244</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>11</v>
@@ -5664,7 +5664,7 @@
         <v>9</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>11</v>
@@ -5681,10 +5681,10 @@
         <v>248</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>11</v>
@@ -5704,7 +5704,7 @@
         <v>20</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>11</v>
@@ -5721,10 +5721,10 @@
         <v>252</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>11</v>
@@ -5744,7 +5744,7 @@
         <v>9</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>11</v>
@@ -5761,10 +5761,10 @@
         <v>256</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>11</v>
@@ -5801,10 +5801,10 @@
         <v>260</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -5824,7 +5824,7 @@
         <v>9</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -5841,10 +5841,10 @@
         <v>264</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>11</v>
@@ -5864,7 +5864,7 @@
         <v>20</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>11</v>
@@ -5881,7 +5881,7 @@
         <v>268</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>10</v>
@@ -5904,7 +5904,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>11</v>
@@ -5921,7 +5921,7 @@
         <v>272</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>21</v>
@@ -5944,7 +5944,7 @@
         <v>20</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>11</v>
@@ -5961,7 +5961,7 @@
         <v>276</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>21</v>
@@ -5984,7 +5984,7 @@
         <v>9</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>11</v>
@@ -6001,10 +6001,10 @@
         <v>280</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>11</v>
@@ -6024,7 +6024,7 @@
         <v>20</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>11</v>
@@ -6041,7 +6041,7 @@
         <v>284</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>21</v>
@@ -6064,7 +6064,7 @@
         <v>9</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>11</v>
@@ -6081,7 +6081,7 @@
         <v>288</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>21</v>
@@ -6104,7 +6104,7 @@
         <v>20</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>11</v>
@@ -6121,10 +6121,10 @@
         <v>292</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>11</v>
@@ -6144,7 +6144,7 @@
         <v>9</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>11</v>
@@ -6161,7 +6161,7 @@
         <v>296</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>10</v>
@@ -6184,7 +6184,7 @@
         <v>20</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>11</v>
@@ -6201,10 +6201,10 @@
         <v>300</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>11</v>
@@ -6224,7 +6224,7 @@
         <v>9</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>11</v>
@@ -6241,10 +6241,10 @@
         <v>304</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>11</v>
@@ -6281,10 +6281,10 @@
         <v>308</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>11</v>
@@ -6304,7 +6304,7 @@
         <v>9</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>11</v>
@@ -6321,10 +6321,10 @@
         <v>312</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>11</v>
@@ -6344,7 +6344,7 @@
         <v>20</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>11</v>
@@ -6361,10 +6361,10 @@
         <v>316</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>11</v>
@@ -6384,7 +6384,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>11</v>
@@ -6401,10 +6401,10 @@
         <v>320</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>11</v>
@@ -6441,10 +6441,10 @@
         <v>324</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>11</v>
@@ -6464,7 +6464,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>11</v>
@@ -6481,10 +6481,10 @@
         <v>328</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>11</v>
@@ -6521,10 +6521,10 @@
         <v>332</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>11</v>
@@ -6544,7 +6544,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>11</v>
@@ -6561,10 +6561,10 @@
         <v>336</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>11</v>
@@ -6584,7 +6584,7 @@
         <v>20</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>11</v>
@@ -6604,7 +6604,7 @@
         <v>9</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>11</v>
@@ -6621,10 +6621,10 @@
         <v>343</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>11</v>
@@ -6641,10 +6641,10 @@
         <v>345</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>11</v>
@@ -6684,7 +6684,7 @@
         <v>9</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>11</v>
@@ -6701,10 +6701,10 @@
         <v>351</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>11</v>
@@ -6721,10 +6721,10 @@
         <v>353</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>11</v>
@@ -6744,7 +6744,7 @@
         <v>20</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>11</v>
@@ -6764,7 +6764,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>152</v>
+        <v>10</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>11</v>
@@ -6781,10 +6781,10 @@
         <v>359</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>11</v>
@@ -6801,10 +6801,10 @@
         <v>361</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>11</v>
@@ -6824,7 +6824,7 @@
         <v>20</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>11</v>
@@ -6844,7 +6844,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>11</v>
@@ -6861,10 +6861,10 @@
         <v>367</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>11</v>
@@ -6881,10 +6881,10 @@
         <v>369</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>11</v>
@@ -6924,7 +6924,7 @@
         <v>9</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>11</v>
@@ -6941,10 +6941,10 @@
         <v>375</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>11</v>
@@ -6961,10 +6961,10 @@
         <v>377</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>11</v>
@@ -6984,7 +6984,7 @@
         <v>20</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>11</v>
@@ -7004,7 +7004,7 @@
         <v>9</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>11</v>
@@ -7021,10 +7021,10 @@
         <v>383</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>11</v>
@@ -7041,10 +7041,10 @@
         <v>385</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>11</v>
@@ -7064,7 +7064,7 @@
         <v>20</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>11</v>
@@ -7084,7 +7084,7 @@
         <v>9</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>11</v>
@@ -7101,10 +7101,10 @@
         <v>391</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>11</v>
@@ -7121,10 +7121,10 @@
         <v>393</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>11</v>
@@ -7144,7 +7144,7 @@
         <v>20</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>11</v>
@@ -7181,10 +7181,10 @@
         <v>399</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>11</v>
@@ -7201,10 +7201,10 @@
         <v>401</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>11</v>
@@ -7224,7 +7224,7 @@
         <v>20</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>11</v>
@@ -7261,10 +7261,10 @@
         <v>407</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>11</v>
@@ -7281,10 +7281,10 @@
         <v>409</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>11</v>
@@ -7304,7 +7304,7 @@
         <v>20</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>11</v>
@@ -7341,10 +7341,10 @@
         <v>415</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>11</v>
@@ -7361,10 +7361,10 @@
         <v>417</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>11</v>
@@ -7384,7 +7384,7 @@
         <v>20</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>11</v>
@@ -7404,7 +7404,7 @@
         <v>9</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>11</v>
@@ -7421,10 +7421,10 @@
         <v>423</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>11</v>
@@ -7441,7 +7441,7 @@
         <v>425</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>21</v>
@@ -7484,7 +7484,7 @@
         <v>9</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>11</v>
@@ -7501,10 +7501,10 @@
         <v>431</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>11</v>
@@ -7521,10 +7521,10 @@
         <v>433</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>11</v>
@@ -7544,7 +7544,7 @@
         <v>20</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>11</v>
@@ -7564,7 +7564,7 @@
         <v>9</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>11</v>
@@ -7581,10 +7581,10 @@
         <v>439</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>11</v>
@@ -7604,7 +7604,7 @@
         <v>9</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>11</v>
@@ -7624,7 +7624,7 @@
         <v>9</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>11</v>
@@ -7641,10 +7641,10 @@
         <v>446</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>11</v>
@@ -7661,10 +7661,10 @@
         <v>448</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>11</v>
@@ -7684,7 +7684,7 @@
         <v>9</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>11</v>
@@ -7704,7 +7704,7 @@
         <v>9</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>11</v>
@@ -7721,10 +7721,10 @@
         <v>454</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>11</v>
@@ -7741,10 +7741,10 @@
         <v>456</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>11</v>
@@ -7764,7 +7764,7 @@
         <v>9</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>11</v>
@@ -7784,7 +7784,7 @@
         <v>9</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>11</v>
@@ -7801,10 +7801,10 @@
         <v>462</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>11</v>
@@ -7821,10 +7821,10 @@
         <v>464</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>11</v>
@@ -7844,7 +7844,7 @@
         <v>9</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>11</v>
@@ -7864,7 +7864,7 @@
         <v>9</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>11</v>
@@ -7881,10 +7881,10 @@
         <v>470</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>11</v>
@@ -7901,10 +7901,10 @@
         <v>472</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>11</v>
@@ -7924,7 +7924,7 @@
         <v>9</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>11</v>
@@ -7944,7 +7944,7 @@
         <v>9</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>11</v>
@@ -7961,10 +7961,10 @@
         <v>478</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>11</v>
@@ -7981,10 +7981,10 @@
         <v>480</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>11</v>
@@ -8024,7 +8024,7 @@
         <v>9</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>11</v>
@@ -8041,10 +8041,10 @@
         <v>486</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>11</v>
@@ -8061,10 +8061,10 @@
         <v>488</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>11</v>
@@ -8084,7 +8084,7 @@
         <v>9</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>11</v>
@@ -8121,10 +8121,10 @@
         <v>494</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>11</v>
@@ -8141,10 +8141,10 @@
         <v>496</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>11</v>
@@ -8164,7 +8164,7 @@
         <v>9</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>11</v>
@@ -8184,7 +8184,7 @@
         <v>9</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>11</v>
@@ -8201,7 +8201,7 @@
         <v>502</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>10</v>
@@ -8221,10 +8221,10 @@
         <v>504</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>11</v>
@@ -8264,7 +8264,7 @@
         <v>9</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>11</v>
@@ -8281,10 +8281,10 @@
         <v>510</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>11</v>
@@ -8301,10 +8301,10 @@
         <v>512</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E247" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>11</v>
@@ -8324,7 +8324,7 @@
         <v>9</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>11</v>
@@ -8344,7 +8344,7 @@
         <v>9</v>
       </c>
       <c r="E249" s="4" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>11</v>
@@ -8361,10 +8361,10 @@
         <v>518</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>11</v>
@@ -8381,7 +8381,7 @@
         <v>520</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E251" s="4" t="s">
         <v>21</v>
@@ -8404,7 +8404,7 @@
         <v>9</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>11</v>
@@ -8424,7 +8424,7 @@
         <v>9</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>11</v>
@@ -8441,10 +8441,10 @@
         <v>526</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>11</v>
@@ -8461,10 +8461,10 @@
         <v>528</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>11</v>
@@ -8484,7 +8484,7 @@
         <v>9</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>11</v>
@@ -8504,7 +8504,7 @@
         <v>9</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>11</v>
@@ -8521,10 +8521,10 @@
         <v>534</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>11</v>
@@ -8541,10 +8541,10 @@
         <v>536</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E259" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>11</v>
@@ -8564,7 +8564,7 @@
         <v>9</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>11</v>
@@ -8584,7 +8584,7 @@
         <v>9</v>
       </c>
       <c r="E261" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>11</v>
@@ -8604,7 +8604,7 @@
         <v>9</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>11</v>
@@ -8621,10 +8621,10 @@
         <v>545</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>11</v>
@@ -8641,10 +8641,10 @@
         <v>547</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>11</v>
@@ -8664,7 +8664,7 @@
         <v>20</v>
       </c>
       <c r="E265" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>11</v>
@@ -8701,7 +8701,7 @@
         <v>553</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E267" s="4" t="s">
         <v>10</v>
@@ -8721,10 +8721,10 @@
         <v>555</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>11</v>
@@ -8744,7 +8744,7 @@
         <v>20</v>
       </c>
       <c r="E269" s="4" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>11</v>
@@ -8764,7 +8764,7 @@
         <v>9</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>11</v>
@@ -8781,10 +8781,10 @@
         <v>561</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E271" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>11</v>
@@ -8801,10 +8801,10 @@
         <v>563</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>11</v>
@@ -8824,7 +8824,7 @@
         <v>20</v>
       </c>
       <c r="E273" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>11</v>
@@ -8844,7 +8844,7 @@
         <v>9</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>11</v>
@@ -8861,7 +8861,7 @@
         <v>569</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E275" s="4" t="s">
         <v>10</v>
@@ -8881,10 +8881,10 @@
         <v>571</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>11</v>
@@ -8904,7 +8904,7 @@
         <v>20</v>
       </c>
       <c r="E277" s="4" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>11</v>
@@ -8924,7 +8924,7 @@
         <v>9</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>11</v>
@@ -8941,10 +8941,10 @@
         <v>577</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E279" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>11</v>
@@ -8961,10 +8961,10 @@
         <v>579</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>11</v>
@@ -8984,7 +8984,7 @@
         <v>20</v>
       </c>
       <c r="E281" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>11</v>
@@ -9021,10 +9021,10 @@
         <v>585</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E283" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>11</v>
@@ -9041,10 +9041,10 @@
         <v>587</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>11</v>
@@ -9064,7 +9064,7 @@
         <v>20</v>
       </c>
       <c r="E285" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>11</v>
@@ -9101,10 +9101,10 @@
         <v>593</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E287" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>11</v>
@@ -9121,10 +9121,10 @@
         <v>595</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>11</v>
@@ -9144,7 +9144,7 @@
         <v>20</v>
       </c>
       <c r="E289" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>11</v>
@@ -9164,7 +9164,7 @@
         <v>9</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>11</v>
@@ -9181,10 +9181,10 @@
         <v>601</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E291" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>11</v>
@@ -9201,7 +9201,7 @@
         <v>603</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>10</v>
@@ -9224,7 +9224,7 @@
         <v>20</v>
       </c>
       <c r="E293" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>11</v>
@@ -9244,7 +9244,7 @@
         <v>9</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>11</v>
@@ -9261,7 +9261,7 @@
         <v>609</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E295" s="4" t="s">
         <v>21</v>
@@ -9281,10 +9281,10 @@
         <v>611</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>11</v>
@@ -9304,7 +9304,7 @@
         <v>20</v>
       </c>
       <c r="E297" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>11</v>
@@ -9324,7 +9324,7 @@
         <v>9</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>11</v>
@@ -9341,10 +9341,10 @@
         <v>617</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E299" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>11</v>
@@ -9361,7 +9361,7 @@
         <v>619</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>10</v>
@@ -9401,10 +9401,10 @@
         <v>624</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>11</v>
@@ -9421,10 +9421,10 @@
         <v>626</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E303" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>11</v>
@@ -9444,7 +9444,7 @@
         <v>9</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>11</v>
@@ -9464,7 +9464,7 @@
         <v>20</v>
       </c>
       <c r="E305" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>11</v>
@@ -9481,10 +9481,10 @@
         <v>632</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>11</v>
@@ -9501,10 +9501,10 @@
         <v>634</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E307" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>11</v>
@@ -9524,7 +9524,7 @@
         <v>9</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>11</v>
@@ -9544,7 +9544,7 @@
         <v>20</v>
       </c>
       <c r="E309" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>11</v>
@@ -9561,7 +9561,7 @@
         <v>640</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>10</v>
@@ -9581,10 +9581,10 @@
         <v>642</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E311" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>11</v>
@@ -9604,7 +9604,7 @@
         <v>9</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>11</v>
@@ -9624,7 +9624,7 @@
         <v>20</v>
       </c>
       <c r="E313" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>11</v>
@@ -9641,10 +9641,10 @@
         <v>648</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>11</v>
@@ -9661,10 +9661,10 @@
         <v>650</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E315" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>11</v>
@@ -9684,7 +9684,7 @@
         <v>9</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>11</v>
@@ -9704,7 +9704,7 @@
         <v>20</v>
       </c>
       <c r="E317" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>11</v>
@@ -9721,10 +9721,10 @@
         <v>656</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>11</v>
@@ -9741,10 +9741,10 @@
         <v>658</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E319" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>11</v>
@@ -9784,7 +9784,7 @@
         <v>20</v>
       </c>
       <c r="E321" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>11</v>
@@ -9804,7 +9804,7 @@
         <v>9</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>11</v>
@@ -9824,7 +9824,7 @@
         <v>9</v>
       </c>
       <c r="E323" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>11</v>
@@ -9841,10 +9841,10 @@
         <v>669</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>11</v>
@@ -9861,10 +9861,10 @@
         <v>671</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E325" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>11</v>
@@ -9884,7 +9884,7 @@
         <v>9</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>11</v>
@@ -9904,7 +9904,7 @@
         <v>9</v>
       </c>
       <c r="E327" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>11</v>
@@ -9921,10 +9921,10 @@
         <v>677</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>11</v>
@@ -9941,7 +9941,7 @@
         <v>679</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E329" s="4" t="s">
         <v>10</v>
@@ -9964,7 +9964,7 @@
         <v>9</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>11</v>
@@ -10001,10 +10001,10 @@
         <v>685</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>11</v>
@@ -10021,10 +10021,10 @@
         <v>687</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E333" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>11</v>
@@ -10044,7 +10044,7 @@
         <v>9</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>11</v>
@@ -10064,7 +10064,7 @@
         <v>9</v>
       </c>
       <c r="E335" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>11</v>
@@ -10081,10 +10081,10 @@
         <v>693</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>11</v>
@@ -10101,10 +10101,10 @@
         <v>695</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E337" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>11</v>
@@ -10124,7 +10124,7 @@
         <v>9</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>11</v>
@@ -10144,7 +10144,7 @@
         <v>9</v>
       </c>
       <c r="E339" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>11</v>
@@ -10161,10 +10161,10 @@
         <v>701</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>11</v>
@@ -10181,10 +10181,10 @@
         <v>703</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E341" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>11</v>
@@ -10201,10 +10201,10 @@
         <v>706</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>11</v>
@@ -10221,10 +10221,10 @@
         <v>708</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E343" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>11</v>
@@ -10244,7 +10244,7 @@
         <v>9</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>11</v>
@@ -10264,7 +10264,7 @@
         <v>20</v>
       </c>
       <c r="E345" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>11</v>
@@ -10281,10 +10281,10 @@
         <v>714</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>11</v>
@@ -10301,10 +10301,10 @@
         <v>716</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E347" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>11</v>
@@ -10324,7 +10324,7 @@
         <v>9</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>11</v>
@@ -10344,7 +10344,7 @@
         <v>20</v>
       </c>
       <c r="E349" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>11</v>
@@ -10361,10 +10361,10 @@
         <v>722</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>11</v>
@@ -10381,10 +10381,10 @@
         <v>724</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E351" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>11</v>
@@ -10404,7 +10404,7 @@
         <v>9</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>11</v>
@@ -10424,7 +10424,7 @@
         <v>20</v>
       </c>
       <c r="E353" s="4" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>11</v>
@@ -10441,10 +10441,10 @@
         <v>730</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>11</v>
@@ -10461,10 +10461,10 @@
         <v>732</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E355" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>11</v>
@@ -10484,7 +10484,7 @@
         <v>9</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>11</v>
@@ -10504,7 +10504,7 @@
         <v>20</v>
       </c>
       <c r="E357" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>11</v>
@@ -10521,10 +10521,10 @@
         <v>738</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>11</v>
@@ -10541,10 +10541,10 @@
         <v>740</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E359" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>11</v>
@@ -10564,7 +10564,7 @@
         <v>9</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>11</v>
@@ -10584,7 +10584,7 @@
         <v>20</v>
       </c>
       <c r="E361" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>11</v>
@@ -10621,10 +10621,10 @@
         <v>749</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E363" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>11</v>
@@ -10644,7 +10644,7 @@
         <v>20</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>11</v>
@@ -10661,10 +10661,10 @@
         <v>753</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E365" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>11</v>
@@ -10684,7 +10684,7 @@
         <v>20</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>11</v>
@@ -10701,10 +10701,10 @@
         <v>757</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E367" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>11</v>
@@ -10724,7 +10724,7 @@
         <v>20</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>11</v>
@@ -10741,7 +10741,7 @@
         <v>761</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E369" s="4" t="s">
         <v>10</v>
@@ -10764,7 +10764,7 @@
         <v>20</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>11</v>
@@ -10781,10 +10781,10 @@
         <v>765</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E371" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>11</v>
@@ -10804,7 +10804,7 @@
         <v>20</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>11</v>
@@ -10821,10 +10821,10 @@
         <v>769</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E373" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>11</v>
@@ -10844,7 +10844,7 @@
         <v>20</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>11</v>
@@ -10861,7 +10861,7 @@
         <v>773</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E375" s="4" t="s">
         <v>21</v>
@@ -10884,7 +10884,7 @@
         <v>20</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>11</v>
@@ -10901,7 +10901,7 @@
         <v>777</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E377" s="4" t="s">
         <v>10</v>
@@ -10924,7 +10924,7 @@
         <v>20</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>11</v>
@@ -10941,10 +10941,10 @@
         <v>781</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E379" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>11</v>
@@ -10981,10 +10981,10 @@
         <v>785</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E381" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>11</v>
@@ -11001,7 +11001,7 @@
         <v>788</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>10</v>
@@ -11024,7 +11024,7 @@
         <v>20</v>
       </c>
       <c r="E383" s="4" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>11</v>
@@ -11041,10 +11041,10 @@
         <v>792</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>11</v>
@@ -11064,7 +11064,7 @@
         <v>20</v>
       </c>
       <c r="E385" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>11</v>
@@ -11081,10 +11081,10 @@
         <v>796</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>11</v>
@@ -11104,7 +11104,7 @@
         <v>20</v>
       </c>
       <c r="E387" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>11</v>
@@ -11121,10 +11121,10 @@
         <v>800</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>11</v>
@@ -11161,10 +11161,10 @@
         <v>804</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>11</v>
@@ -11184,7 +11184,7 @@
         <v>20</v>
       </c>
       <c r="E391" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>11</v>
@@ -11201,10 +11201,10 @@
         <v>808</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>11</v>
@@ -11224,7 +11224,7 @@
         <v>20</v>
       </c>
       <c r="E393" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>11</v>
@@ -11241,10 +11241,10 @@
         <v>812</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>11</v>
@@ -11264,7 +11264,7 @@
         <v>20</v>
       </c>
       <c r="E395" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>11</v>
@@ -11281,10 +11281,10 @@
         <v>816</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>11</v>
@@ -11304,7 +11304,7 @@
         <v>20</v>
       </c>
       <c r="E397" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>11</v>
@@ -11321,10 +11321,10 @@
         <v>820</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>11</v>
@@ -11344,7 +11344,7 @@
         <v>20</v>
       </c>
       <c r="E399" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>11</v>
@@ -11361,10 +11361,10 @@
         <v>824</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>11</v>
@@ -11384,7 +11384,7 @@
         <v>20</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>11</v>
@@ -11401,10 +11401,10 @@
         <v>829</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F402" s="3" t="s">
         <v>11</v>
@@ -11441,10 +11441,10 @@
         <v>833</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>11</v>
@@ -11464,7 +11464,7 @@
         <v>20</v>
       </c>
       <c r="E405" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>11</v>
@@ -11481,10 +11481,10 @@
         <v>837</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="F406" s="3" t="s">
         <v>11</v>
@@ -11504,7 +11504,7 @@
         <v>9</v>
       </c>
       <c r="E407" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F407" s="3" t="s">
         <v>11</v>
@@ -11521,10 +11521,10 @@
         <v>841</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F408" s="3" t="s">
         <v>11</v>
@@ -11544,7 +11544,7 @@
         <v>20</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F409" s="3" t="s">
         <v>11</v>
@@ -11561,10 +11561,10 @@
         <v>845</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F410" s="3" t="s">
         <v>11</v>
@@ -11584,7 +11584,7 @@
         <v>9</v>
       </c>
       <c r="E411" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>11</v>
@@ -11601,10 +11601,10 @@
         <v>849</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>11</v>
@@ -11624,7 +11624,7 @@
         <v>20</v>
       </c>
       <c r="E413" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F413" s="3" t="s">
         <v>11</v>
@@ -11641,10 +11641,10 @@
         <v>853</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>11</v>
@@ -11664,7 +11664,7 @@
         <v>9</v>
       </c>
       <c r="E415" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F415" s="3" t="s">
         <v>11</v>
@@ -11681,7 +11681,7 @@
         <v>857</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>21</v>
@@ -11704,7 +11704,7 @@
         <v>20</v>
       </c>
       <c r="E417" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F417" s="3" t="s">
         <v>11</v>
@@ -11721,10 +11721,10 @@
         <v>861</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F418" s="3" t="s">
         <v>11</v>
@@ -11744,7 +11744,7 @@
         <v>9</v>
       </c>
       <c r="E419" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F419" s="3" t="s">
         <v>11</v>
@@ -11761,10 +11761,10 @@
         <v>865</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F420" s="3" t="s">
         <v>11</v>
@@ -11784,7 +11784,7 @@
         <v>20</v>
       </c>
       <c r="E421" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F421" s="3" t="s">
         <v>11</v>
@@ -11804,7 +11804,7 @@
         <v>9</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F422" s="3" t="s">
         <v>11</v>
@@ -11824,7 +11824,7 @@
         <v>9</v>
       </c>
       <c r="E423" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F423" s="3" t="s">
         <v>11</v>
@@ -11841,10 +11841,10 @@
         <v>874</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F424" s="3" t="s">
         <v>11</v>
@@ -11861,10 +11861,10 @@
         <v>876</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E425" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>11</v>
@@ -11884,7 +11884,7 @@
         <v>9</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>11</v>
@@ -11904,7 +11904,7 @@
         <v>9</v>
       </c>
       <c r="E427" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>11</v>
@@ -11921,10 +11921,10 @@
         <v>882</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>11</v>
@@ -11941,10 +11941,10 @@
         <v>884</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E429" s="4" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>11</v>
@@ -11964,7 +11964,7 @@
         <v>9</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>11</v>
@@ -11984,7 +11984,7 @@
         <v>9</v>
       </c>
       <c r="E431" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>11</v>
@@ -12001,10 +12001,10 @@
         <v>890</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>11</v>
@@ -12021,10 +12021,10 @@
         <v>892</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E433" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>11</v>
@@ -12044,7 +12044,7 @@
         <v>9</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>11</v>
@@ -12064,7 +12064,7 @@
         <v>9</v>
       </c>
       <c r="E435" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>11</v>
@@ -12081,7 +12081,7 @@
         <v>898</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>21</v>
@@ -12101,10 +12101,10 @@
         <v>900</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E437" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F437" s="3" t="s">
         <v>11</v>
@@ -12144,7 +12144,7 @@
         <v>9</v>
       </c>
       <c r="E439" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F439" s="3" t="s">
         <v>11</v>
@@ -12161,10 +12161,10 @@
         <v>906</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F440" s="3" t="s">
         <v>11</v>
@@ -12181,10 +12181,10 @@
         <v>908</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E441" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F441" s="3" t="s">
         <v>11</v>
@@ -12204,7 +12204,7 @@
         <v>9</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F442" s="3" t="s">
         <v>11</v>
@@ -12224,7 +12224,7 @@
         <v>9</v>
       </c>
       <c r="E443" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F443" s="3" t="s">
         <v>11</v>
@@ -12241,10 +12241,10 @@
         <v>914</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F444" s="3" t="s">
         <v>11</v>
@@ -12261,7 +12261,7 @@
         <v>916</v>
       </c>
       <c r="D445" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E445" s="4" t="s">
         <v>21</v>
@@ -12284,7 +12284,7 @@
         <v>9</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F446" s="3" t="s">
         <v>11</v>
@@ -12304,7 +12304,7 @@
         <v>9</v>
       </c>
       <c r="E447" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>11</v>
@@ -12321,10 +12321,10 @@
         <v>922</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>11</v>
@@ -12341,10 +12341,10 @@
         <v>924</v>
       </c>
       <c r="D449" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E449" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>11</v>
@@ -12364,7 +12364,7 @@
         <v>9</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="F450" s="3" t="s">
         <v>11</v>
@@ -12401,10 +12401,10 @@
         <v>930</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F452" s="3" t="s">
         <v>11</v>
@@ -12421,10 +12421,10 @@
         <v>932</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E453" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>11</v>
@@ -12444,7 +12444,7 @@
         <v>9</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>152</v>
+        <v>10</v>
       </c>
       <c r="F454" s="3" t="s">
         <v>11</v>
@@ -12464,7 +12464,7 @@
         <v>9</v>
       </c>
       <c r="E455" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F455" s="3" t="s">
         <v>11</v>
@@ -12481,10 +12481,10 @@
         <v>938</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F456" s="3" t="s">
         <v>11</v>
@@ -12501,10 +12501,10 @@
         <v>940</v>
       </c>
       <c r="D457" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E457" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F457" s="3" t="s">
         <v>11</v>
@@ -12524,7 +12524,7 @@
         <v>9</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F458" s="3" t="s">
         <v>11</v>
@@ -12544,7 +12544,7 @@
         <v>9</v>
       </c>
       <c r="E459" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F459" s="3" t="s">
         <v>11</v>
@@ -12561,10 +12561,10 @@
         <v>946</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F460" s="3" t="s">
         <v>11</v>
@@ -12581,10 +12581,10 @@
         <v>948</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E461" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>11</v>
@@ -12624,7 +12624,7 @@
         <v>9</v>
       </c>
       <c r="E463" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F463" s="3" t="s">
         <v>11</v>
@@ -12641,10 +12641,10 @@
         <v>954</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F464" s="3" t="s">
         <v>11</v>
@@ -12661,10 +12661,10 @@
         <v>956</v>
       </c>
       <c r="D465" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E465" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F465" s="3" t="s">
         <v>11</v>
@@ -12684,7 +12684,7 @@
         <v>9</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F466" s="3" t="s">
         <v>11</v>
@@ -12704,7 +12704,7 @@
         <v>9</v>
       </c>
       <c r="E467" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F467" s="3" t="s">
         <v>11</v>
@@ -12721,10 +12721,10 @@
         <v>962</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>11</v>
@@ -12741,10 +12741,10 @@
         <v>964</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E469" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F469" s="3" t="s">
         <v>11</v>
@@ -12764,7 +12764,7 @@
         <v>9</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F470" s="3" t="s">
         <v>11</v>
@@ -12784,7 +12784,7 @@
         <v>9</v>
       </c>
       <c r="E471" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F471" s="3" t="s">
         <v>11</v>
